--- a/template_boc12.xlsx
+++ b/template_boc12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andrew\Desktop\боц\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F1986E82-5740-4A9A-8983-7CBD7A0B739C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DDA8415-96A0-4240-B655-C95E614A2CBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6345" yWindow="4215" windowWidth="21600" windowHeight="11385" xr2:uid="{ADCE18E3-64A2-4CA2-9C29-1ED7F8C19B21}"/>
+    <workbookView xWindow="4125" yWindow="1875" windowWidth="21600" windowHeight="11385" xr2:uid="{ADCE18E3-64A2-4CA2-9C29-1ED7F8C19B21}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -771,31 +771,30 @@
         <v>160</v>
       </c>
     </row>
-    <row r="17" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>160</v>
       </c>
     </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>160</v>
       </c>
     </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>160</v>
       </c>
     </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>160</v>
       </c>
     </row>
-    <row r="23" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B23" s="1"/>
+    <row r="23" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="B23" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
@@ -806,10 +805,10 @@
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
-      <c r="M23" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="N23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
@@ -820,10 +819,10 @@
       <c r="V23" s="1"/>
       <c r="W23" s="1"/>
       <c r="X23" s="1"/>
-      <c r="Y23" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z23" s="1"/>
+      <c r="Y23" s="1"/>
+      <c r="Z23" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="AA23" s="1"/>
       <c r="AB23" s="1"/>
       <c r="AC23" s="1"/>
@@ -834,122 +833,123 @@
       <c r="AH23" s="1"/>
       <c r="AI23" s="1"/>
       <c r="AJ23" s="1"/>
-    </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>1</v>
-      </c>
+      <c r="AK23" s="1"/>
+    </row>
+    <row r="24" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D24">
+        <v>3</v>
+      </c>
+      <c r="E24">
         <v>4</v>
       </c>
-      <c r="E24">
+      <c r="F24">
         <v>5</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <v>6</v>
       </c>
-      <c r="G24">
+      <c r="H24">
         <v>7</v>
       </c>
-      <c r="H24">
+      <c r="I24">
         <v>8</v>
       </c>
-      <c r="I24">
+      <c r="J24">
         <v>9</v>
       </c>
-      <c r="J24">
+      <c r="K24">
         <v>10</v>
       </c>
-      <c r="K24">
+      <c r="L24">
         <v>11</v>
       </c>
-      <c r="L24">
+      <c r="M24">
         <v>12</v>
       </c>
-      <c r="M24">
-        <v>1</v>
-      </c>
       <c r="N24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P24">
+        <v>3</v>
+      </c>
+      <c r="Q24">
         <v>4</v>
       </c>
-      <c r="Q24">
+      <c r="R24">
         <v>5</v>
       </c>
-      <c r="R24">
+      <c r="S24">
         <v>6</v>
       </c>
-      <c r="S24">
+      <c r="T24">
         <v>7</v>
       </c>
-      <c r="T24">
+      <c r="U24">
         <v>8</v>
       </c>
-      <c r="U24">
+      <c r="V24">
         <v>9</v>
       </c>
-      <c r="V24">
+      <c r="W24">
         <v>10</v>
       </c>
-      <c r="W24">
+      <c r="X24">
         <v>11</v>
       </c>
-      <c r="X24">
+      <c r="Y24">
         <v>12</v>
       </c>
-      <c r="Y24">
-        <v>1</v>
-      </c>
       <c r="Z24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB24">
+        <v>3</v>
+      </c>
+      <c r="AC24">
         <v>4</v>
       </c>
-      <c r="AC24">
+      <c r="AD24">
         <v>5</v>
       </c>
-      <c r="AD24">
+      <c r="AE24">
         <v>6</v>
       </c>
-      <c r="AE24">
+      <c r="AF24">
         <v>7</v>
       </c>
-      <c r="AF24">
+      <c r="AG24">
         <v>8</v>
       </c>
-      <c r="AG24">
+      <c r="AH24">
         <v>9</v>
       </c>
-      <c r="AH24">
+      <c r="AI24">
         <v>10</v>
       </c>
-      <c r="AI24">
+      <c r="AJ24">
         <v>11</v>
       </c>
-      <c r="AJ24">
+      <c r="AK24">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A23:L23"/>
-    <mergeCell ref="M23:X23"/>
-    <mergeCell ref="Y23:AJ23"/>
+    <mergeCell ref="B23:M23"/>
+    <mergeCell ref="N23:Y23"/>
+    <mergeCell ref="Z23:AK23"/>
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="N1:Y1"/>
     <mergeCell ref="Z1:AK1"/>
